--- a/ig/DM_FINESS_New/ValueSet-jdv-j359-autorite-enregistrement-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j359-autorite-enregistrement-finess.xlsx
@@ -96,7 +96,7 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>AutoriteEnregistrementFiness</t>
+    <t>autoriteEnregistrementFiness</t>
   </si>
   <si>
     <t>=</t>
